--- a/docs/cells/tropical_cyclone_wind_real_estate/proposed/damage_curve_records_tropical_cyclone_wind_real_estate__model_v0_1__docs_r1.xlsx
+++ b/docs/cells/tropical_cyclone_wind_real_estate/proposed/damage_curve_records_tropical_cyclone_wind_real_estate__model_v0_1__docs_r1.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="curve_records" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="reference_buildings" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="wind_characteristics" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="sources" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="claims" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="parameter_tiers" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="value_crosswalk" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="variant_sensitivity" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="known_answer_tests" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="curve_records" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reference_buildings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="wind_characteristics" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sources" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="claims" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="parameter_tiers" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="value_crosswalk" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variant_sensitivity" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="known_answer_tests" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27385,7 +27385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -28256,6 +28256,93 @@
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TCRE-S010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Hazard_Modeling. Real-estate reference profiles r1 (reference_candidates.yml and generated profile views), handoff of 2026-10-16.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://github.com/aamani-ai/Hazard_Modeling/blob/8b0d61c88fbcf85daa1c098516cee22398cdb524/docs/plans/_cross_cutting/real_estate_conus/reference_candidates.yml</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>commit 8b0d61c88fbcf85daa1c098516cee22398cdb524; reference_candidates.yml git blob a74fb72b0a2edce593b5505e0fd8852f4c0253f8; profiles re_house_1s_wood_slab, re_warehouse_1s_steel_slab, re_office_3s_slab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>internal design input</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>selector_archetype;value_basis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>tropical_cyclone_wind</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>T4_placeholder_or_expert_judgment</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>declared physical target per reference building: storeys, structure, roof cover and age, wall system, window-to-wall ratio, opening protection, large doors, floor area, replacement budget</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Bind curve records to the profiles and read the wind characteristics the profiles state.</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Treat the profiles as observed buildings, their ages as code-compliance evidence, or the budgets as qualified coverage.</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>adopt</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Declared design, not evidence of damage. Binding in PROFILE_BINDING_tropical_cyclone_wind_real_estate__model_v0_2__docs_r1.md.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -28268,7 +28355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -29946,6 +30033,475 @@
       <c r="M25" t="inlineStr">
         <is>
           <t>FEMA documents the reason or corrects the rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TCRE-C025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>tropical_cyclone_wind</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SECBM is the steel engineered commercial building of 3-5 stories (SECBL 1-2, SECBH 6 or more); the extract publishes 96 SECBM variants. For single-ply membrane, medium window area, no shutters, debris environment B and standard metal deck, SECBM and MECBM (masonry) give the same loss ratio at 100-160 mph in open and suburban terrain.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>direct_observation</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>TCRE-S001;TCRE-S002</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>TM Appendix B building-type list (PDF p. 678, 33_SECBM); extract huListOfWindBldgTypes wbID 1840; VARIANT_SENSITIVITY_tropical_cyclone_wind_real_estate__model_v0_2__docs_r1.csv</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>T2_public_lab_standard_or_physics</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>office building type</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>adopt</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Use SECBM for the three-storey office; record the masonry equivalence at the sampled speeds.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Use SECBL for a three-storey building; claim full SECBM/MECBM identity beyond the sampled speeds.</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>The office has 3 storeys; the v0.1 commercial type (SECBL) is for 1-2.</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>A height- or curtain-wall-specific source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TCRE-C026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>tropical_cyclone_wind</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Hazus window-area classes for engineered buildings are low (&lt;25%), medium (25-40%) and high (&gt;40%) of the wall area.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>direct_observation</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>TCRE-S001</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Hazus 7.0 TM §9.6.10, p. 9-38</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>T2_public_lab_standard_or_physics</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>office window area</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>adopt</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Map the profile's 33% window-to-wall ratio to medium.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Use the most-common value (low) when the profile states the ratio.</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>The profile states the ratio; the class follows by definition.</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>A profile revision changes the ratio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TCRE-C027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>tropical_cyclone_wind</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Hazus 6.1 assigns the metal roof deck age 'new or average' to metal roofs installed in 2008 or later and 'old' to those installed before 2008.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>direct_observation</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>TCRE-S001</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Hazus 7.0 TM §9.6.6, p. 9-37</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>T2_public_lab_standard_or_physics</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>warehouse roof deck age</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>adopt</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Map the profile's 10-year roof cover age (installed about 2016) to new or average.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Read the declared synthetic age as an observed installation date.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>The profile states the roof age; the class follows from FEMA's rule.</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>A profile revision changes the roof age or its meaning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TCRE-C028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>tropical_cyclone_wind</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Hazus SPMB (pre-engineered metal building) characteristics are roof-deck age, shutters and metal-deck attachment only; there is no characteristic for large overhead doors, so the profile's eight 12 x 14 ft unprotected doors cannot change the curve.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>direct_observation</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>TCRE-S001;TCRE-S002</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Hazus 7.0 TM WBC list p. 9-32; extract huListOfWindBldgTypes SPMBL (8 variants)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>T2_public_lab_standard_or_physics</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>warehouse large doors</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>adopt_with_limits</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Record large doors as a known limit of the source class average.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Claim the curve accounts for the door openings.</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>The source has no door attribute.</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>A source with large-door or opening-ratio variants.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TCRE-C029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>tropical_cyclone_wind</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Hazus assigns house roof-deck attachment and roof-to-wall connection from the building code, design wind speed, design terrain and code year, so a 20-year-old house is code-built (8d nails, straps) only where its local code required it. On the source curves, 8d @ 6"/12" with straps reads 19.0% at 120 mph open (reference 31.3%) and 21.5% at 140 mph suburban (reference 51.2%).</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>computed_check</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>TCRE-S001;TCRE-S002</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Hazus 7.0 TM §9.6.5 and §9.6.9, Figures 9-12 and 9-13, pp. 9-36 to 9-38; VARIANT_SENSITIVITY_tropical_cyclone_wind_real_estate__model_v0_2__docs_r1.csv</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>T3_engineering_proxy_or_adjacent_empirical</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>house wind characteristics</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>reference_only</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Keep the national most-common connections for the CONUS reference house and state the code-built values as a sensitivity.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Pick code-built connections for every cell, or claim the reference house reflects local code.</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>One reference house is placed at every cell; the code-dependent choice varies by location.</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Hazard supplies a design-wind or code zone per cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TCRE-C030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>tropical_cyclone_wind</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Effect of the v0.2 selections on the source curves: office SECBM single-ply membrane medium windows reads 14.0% at 120 mph open (v0.1 commercial SECBL 8.8%); warehouse new-or-average deck reads 23.5% at 120 mph open and 5.2% suburban (old deck 39.5% and 12.7%). As for SECBL, the office reads higher in light-suburban than in open terrain (17.4% vs 14.0% at 120 mph).</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>computed_check</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>TCRE-S002</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>VARIANT_SENSITIVITY_tropical_cyclone_wind_real_estate__model_v0_2__docs_r1.csv</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>T2_public_lab_standard_or_physics</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>v0.2 selection effect</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>adopt</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Report the change from v0.1 and the terrain ordering.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Read the terrain ordering as physical.</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Values read from the governed extract; cross-checked against SimCenter.</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>A newer Hazus extract.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TCRE-C031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>tropical_cyclone_wind</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>The v0.2 records keep every published value; their dips are at most 0.0035 (office, 205 mph light-suburban), and the new warehouse record dips by at most 0.0004 at 185-190 mph, below the 200 mph seen in v0.1.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>computed_check</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>TCRE-S002</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>CURVE_ORDINATES_tropical_cyclone_wind_real_estate__model_v0_2__docs_r1.csv</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>T2_public_lab_standard_or_physics</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>record form</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>adopt</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Keep the published values with straight lines between them; flag records with dips.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Repair dips with a running maximum or a smooth fit.</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Simulation noise far below any decision threshold; same practice as D-TCRE-17.</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>A selected record dips by more than 0.005.</t>
         </is>
       </c>
     </row>
